--- a/1150080143_VoAnhKiet.xlsx
+++ b/1150080143_VoAnhKiet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Software-Testing\Buoi2\1150080143_VoAnhKiet_CNPM2_Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB15E8EB-B38D-4855-AC44-5BEFA35339E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1759DC7A-9757-4E45-9E6D-D97EE03CAD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{4DCF6CBE-5135-4433-8EE3-D3D0176D38E0}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{4DCF6CBE-5135-4433-8EE3-D3D0176D38E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Bài 1" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="247">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -540,6 +540,252 @@
   </si>
   <si>
     <t>Hệ thống báo lỗi/Yêu cầu nhập ngày</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài chuỗi số nguyên nhập vào ([1-10] hoặc [20-30])</t>
+  </si>
+  <si>
+    <t>Thiết kế test case cho trường nhập liệu số nguyên có giới hạn độ dài ký tự theo hai khoảng [1-10] và [20-30].</t>
+  </si>
+  <si>
+    <t>Dãy số nguyên bất kỳ.</t>
+  </si>
+  <si>
+    <t>Độ dài của dãy số nhập vào.</t>
+  </si>
+  <si>
+    <t>Độ dài X &lt; 1 (Để trống)</t>
+  </si>
+  <si>
+    <t>Vùng 2 (Hợp lệ):</t>
+  </si>
+  <si>
+    <t>Độ dài 1 ≤ X ≤ 10</t>
+  </si>
+  <si>
+    <t>Vùng 3 (Không hợp lệ):</t>
+  </si>
+  <si>
+    <t>Độ dài 10 &lt; X &lt; 20</t>
+  </si>
+  <si>
+    <t>Vùng 4 (Hợp lệ):</t>
+  </si>
+  <si>
+    <t>Độ dài 20 ≤ X ≤ 30</t>
+  </si>
+  <si>
+    <t>Độ dài X &gt; 30</t>
+  </si>
+  <si>
+    <t>Ký tự không phải số nguyên (Chữ, số thập phân, ký tự đặc biệt)</t>
+  </si>
+  <si>
+    <t>Kiểm tra trường hợp để trống (X &lt; 1)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài nhỏ nhất vùng 2 (X = 1)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài giữa vùng 2 (X = 5)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài lớn nhất vùng 2 (X = 10)</t>
+  </si>
+  <si>
+    <t>Kiểm tra sát biên vùng 3 (X = 11)</t>
+  </si>
+  <si>
+    <t>Kiểm tra giá trị giữa vùng 3 (X = 15)</t>
+  </si>
+  <si>
+    <t>Kiểm tra sát biên dưới vùng 4 (X = 20)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài giữa vùng 4 (X = 25)</t>
+  </si>
+  <si>
+    <t>(Dãy số dài 25 ký tự)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài lớn nhất vùng 4 (X = 30)</t>
+  </si>
+  <si>
+    <t>(Dãy số dài 30 ký tự)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài vượt quá vùng 4 (X = 31)</t>
+  </si>
+  <si>
+    <t>(Dãy số dài 31 ký tự)</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập ký tự không phải số</t>
+  </si>
+  <si>
+    <t>"abcde123"</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập số thập phân</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi (Chỉ nhận số nguyên)</t>
+  </si>
+  <si>
+    <t>Kiểm tra hệ thống thống kê và phân tích điểm sinh viên</t>
+  </si>
+  <si>
+    <t>Thiết kế tập dữ liệu thử nghiệm để kiểm tra tính năng tính điểm trung bình, phân loại giới tính và đếm số sinh viên lên lớp.</t>
+  </si>
+  <si>
+    <t>File dữ liệu đã được khởi tạo đúng định dạng.</t>
+  </si>
+  <si>
+    <t>Chương trình có quyền đọc file đầu vào.</t>
+  </si>
+  <si>
+    <t>Số lượng dòng trong file (N).</t>
+  </si>
+  <si>
+    <t>Tên sinh viên, Giới tính, Điểm 5 môn.</t>
+  </si>
+  <si>
+    <t>Vùng 1 (Hợp lệ):</t>
+  </si>
+  <si>
+    <t>Số dòng 1≤N≤100; Tên ≤20 ký tự; Điểm [0−10]</t>
+  </si>
+  <si>
+    <t>Vùng 2 (Không hợp lệ):</t>
+  </si>
+  <si>
+    <t>File trống (N=0) hoặc số dòng N&gt;100</t>
+  </si>
+  <si>
+    <t>Tên sinh viên &gt;20 ký tự</t>
+  </si>
+  <si>
+    <t>Giới tính sai định dạng (Trống hoặc &gt;1 ký tự)</t>
+  </si>
+  <si>
+    <t>Điểm số nằm ngoài khoảng [0−10] (Ví dụ: -1 hoặc 11)</t>
+  </si>
+  <si>
+    <t>Kiểm tra file có 1 dòng hợp lệ</t>
+  </si>
+  <si>
+    <t>N=1, Tên="An", GT="M", Điểm={8,8,8,8,8}</t>
+  </si>
+  <si>
+    <t>ĐTB=8.0, Lên lớp: 1</t>
+  </si>
+  <si>
+    <t>Kiểm tra biên trên số lượng dòng</t>
+  </si>
+  <si>
+    <t>N=100 dòng sinh viên hợp lệ</t>
+  </si>
+  <si>
+    <t>Tính toán đúng cho 100 SV</t>
+  </si>
+  <si>
+    <t>Kiểm tra biên độ dài tên (20 ký tự)</t>
+  </si>
+  <si>
+    <t>Tên="Nguyen Hoang Anh Tuyet" (20)</t>
+  </si>
+  <si>
+    <t>Hệ thống chấp nhận và xử lý</t>
+  </si>
+  <si>
+    <t>Kiểm tra tên vượt quá 20 ký tự</t>
+  </si>
+  <si>
+    <t>Tên="Phan Hoang Nguyen Ngoc Han"</t>
+  </si>
+  <si>
+    <t>Báo lỗi tên quá dài</t>
+  </si>
+  <si>
+    <t>Kiểm tra điểm biên nhỏ nhất</t>
+  </si>
+  <si>
+    <t>Điểm={0,0,0,0,0}</t>
+  </si>
+  <si>
+    <t>ĐTB=0, Lên lớp: 0</t>
+  </si>
+  <si>
+    <t>Kiểm tra điểm biên lớn nhất</t>
+  </si>
+  <si>
+    <t>Điểm={10,10,10,10,10}</t>
+  </si>
+  <si>
+    <t>ĐTB=10, Lên lớp: 1</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic lên lớp (ĐTB sát 5)</t>
+  </si>
+  <si>
+    <t>Điểm={5,5,5,5,5.1} (ĐTB=5.02)</t>
+  </si>
+  <si>
+    <t>ĐTB &gt; 5: Lên lớp</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic ở lại lớp (ĐTB = 5)</t>
+  </si>
+  <si>
+    <t>Điểm={5,5,5,5,5} (ĐTB=5.0)</t>
+  </si>
+  <si>
+    <t>Không tính là lên lớp (phải &gt;5)</t>
+  </si>
+  <si>
+    <t>Kiểm tra giới tính không hợp lệ</t>
+  </si>
+  <si>
+    <t>GT="Nam" (Dài hơn 1 ký tự)</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi định dạng GT</t>
+  </si>
+  <si>
+    <t>Kiểm tra điểm ngoài khoảng (quá cao)</t>
+  </si>
+  <si>
+    <t>Điểm={11,8,7,9,10}</t>
+  </si>
+  <si>
+    <t>Báo lỗi điểm không hợp lệ</t>
+  </si>
+  <si>
+    <t>Kiểm tra file trống</t>
+  </si>
+  <si>
+    <t>N=0</t>
+  </si>
+  <si>
+    <t>Thông báo: "Không có dữ liệu"</t>
+  </si>
+  <si>
+    <t>Kiểm tra file vượt quá 100 dòng</t>
+  </si>
+  <si>
+    <t>N=101</t>
+  </si>
+  <si>
+    <t>Báo lỗi vượt quá giới hạn file</t>
+  </si>
+  <si>
+    <t>BU_007</t>
+  </si>
+  <si>
+    <t>BU_006</t>
+  </si>
+  <si>
+    <t>BU_005</t>
   </si>
 </sst>
 </file>
@@ -634,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -709,6 +955,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2319,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -2668,18 +2917,767 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7792ED-3732-4922-9A6B-78771CF0673C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.21875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="29.44140625" style="20" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46174</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="22">
+        <v>1</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="22">
+        <v>1</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="22">
+        <v>2</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="22">
+        <v>2</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C14" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C16" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C17" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C18" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C19" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="26"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" s="24">
+        <v>1</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="24">
+        <v>12345</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="24">
+        <v>1234567890</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" s="24">
+        <v>12345678901</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="24">
+        <v>123456789012345</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="24">
+        <v>1.11112222233333E+19</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="27">
+        <v>123456</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5607F8-6129-499C-975B-6751906C3F9C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.21875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="32" style="20" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46174</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="22">
+        <v>1</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="22">
+        <v>1</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="22">
+        <v>2</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="22">
+        <v>2</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C14" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C16" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C17" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C18" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="26"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>243</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>